--- a/tools/promo/pv分鏡.xlsx
+++ b/tools/promo/pv分鏡.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ray Ku\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\TIVOT\tools\promo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63D603E2-C526-4A68-9597-4AACA093C99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFD46FF-40F5-487B-A383-5B78E5C3C955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13470" yWindow="2475" windowWidth="32055" windowHeight="19215" xr2:uid="{910AC4BF-4CE6-42DE-80D7-9A5DDFBC8BA1}"/>
+    <workbookView xWindow="1485" yWindow="2565" windowWidth="21600" windowHeight="11295" xr2:uid="{910AC4BF-4CE6-42DE-80D7-9A5DDFBC8BA1}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="48">
   <si>
     <t>cut</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -86,10 +86,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dreambreaker動畫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>db語音</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -122,14 +118,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>遺跡平移 古城</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遺跡平移 古墓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>蕾娜微笑動畫</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -142,14 +130,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>遊戲畫面 戰鬥</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遊戲畫面  戰鬥</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>主角與賽西莉背靠背動畫</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -170,10 +150,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>未定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>隨機場景快剪0.2秒一張</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -218,7 +194,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>中間隨拍點插入米夏聖徒在85 87秒各閃兩次</t>
+    <t>anya introl動畫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主角查膛動畫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>禍魘大軍動畫 畫面橫移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遺跡平移 上</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遺跡平移 左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遺跡平移 下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遺跡平移 右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>選最有辨識度 視覺效果最佳的圖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中間隨拍點插入米夏聖徒 璐娜動畫 尼莫動畫在拍點秒各閃兩次 停留時間短但是要讓人足夠辨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -226,7 +234,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -603,15 +611,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68D691C7-3077-461C-BA66-9729DA4CB7E2}">
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -631,13 +639,13 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -657,10 +665,10 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -680,7 +688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -691,13 +699,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -708,10 +716,10 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -722,10 +730,10 @@
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
@@ -736,10 +744,10 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -750,10 +758,10 @@
         <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
@@ -764,10 +772,10 @@
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
@@ -778,10 +786,10 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
@@ -792,10 +800,10 @@
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
@@ -806,10 +814,10 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
@@ -820,10 +828,10 @@
         <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>13</v>
       </c>
@@ -834,10 +842,10 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>14</v>
       </c>
@@ -848,10 +856,10 @@
         <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>15</v>
       </c>
@@ -862,10 +870,10 @@
         <v>43</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
@@ -876,10 +884,10 @@
         <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
@@ -890,10 +898,10 @@
         <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
@@ -904,13 +912,10 @@
         <v>49</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
-      </c>
-      <c r="G19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
@@ -921,171 +926,185 @@
         <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G20" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="H20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21">
-        <v>52.1</v>
-      </c>
-      <c r="C21">
-        <v>56</v>
-      </c>
       <c r="D21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="H21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22">
-        <v>56.1</v>
-      </c>
-      <c r="C22">
-        <v>61</v>
-      </c>
       <c r="D22" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="H22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>61.1</v>
+        <v>56.1</v>
       </c>
       <c r="C23">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="H23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>66.099999999999994</v>
+        <v>61.1</v>
       </c>
       <c r="C24">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="C25">
         <v>67</v>
       </c>
-      <c r="C25">
-        <v>71</v>
-      </c>
       <c r="D25" t="s">
-        <v>38</v>
-      </c>
-      <c r="H25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C26">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27">
-        <v>75.099999999999994</v>
+        <v>72</v>
       </c>
       <c r="C27">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28">
-        <v>79.099999999999994</v>
+        <v>75.099999999999994</v>
       </c>
       <c r="C28">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29">
-        <v>83.1</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="C29">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
-      </c>
-      <c r="G29" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H29" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>29</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>83.1</v>
+      </c>
+      <c r="C30">
+        <v>92</v>
+      </c>
+      <c r="D30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8">
       <c r="A32">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
         <v>31</v>
       </c>
     </row>
